--- a/src/test/resources/ERP_E2E.xlsx
+++ b/src/test/resources/ERP_E2E.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="177">
   <si>
     <t>TC_ID</t>
   </si>
@@ -518,6 +518,39 @@
   </si>
   <si>
     <t>INVOICE_00114</t>
+  </si>
+  <si>
+    <t>Dorsey</t>
+  </si>
+  <si>
+    <t>Synergistic Steel Knife</t>
+  </si>
+  <si>
+    <t>IM_PROD_8085</t>
+  </si>
+  <si>
+    <t>CAM00397</t>
+  </si>
+  <si>
+    <t>Campaign_85916</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Carl</t>
+  </si>
+  <si>
+    <t>Meghann Feest</t>
+  </si>
+  <si>
+    <t>Reichert-Orn</t>
+  </si>
+  <si>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>SalesOrder540</t>
   </si>
 </sst>
 </file>
@@ -968,49 +1001,49 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>64</v>
+        <v>171</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="M2" t="s" s="0">
         <v>16</v>
       </c>
       <c r="N2" t="s" s="0">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="O2" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="P2" t="s" s="0">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="Q2" t="s" s="0">
-        <v>165</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
